--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="2"/>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G39" s="2"/>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G43" s="2"/>
     </row>
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.29</v>
       </c>
       <c r="G44" s="2"/>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="G56" s="2"/>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="G59" s="2"/>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" s="2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="G71" s="2"/>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="G83" s="2"/>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G84" s="2"/>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G86" s="2"/>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.23</v>
       </c>
       <c r="G98" s="2"/>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="G103" s="2"/>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" s="2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="G104" s="2"/>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.28</v>
       </c>
       <c r="G113" s="2"/>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G114" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_arica_y_parinacota.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2020_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
